--- a/buckman/output/depletion/TABLE_5_La_Cienega_Springs_2025.xlsx
+++ b/buckman/output/depletion/TABLE_5_La_Cienega_Springs_2025.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,7 +34,20 @@
     </font>
     <font>
       <name val="Aptos"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
@@ -62,15 +77,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -438,11 +459,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -456,221 +480,560 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Annual Δ (AF)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Cumul check</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Δ (B−D)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>2004</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="4" t="n">
         <v>0.45</v>
       </c>
+      <c r="C2" s="5">
+        <f>B2</f>
+        <v/>
+      </c>
+      <c r="D2" s="5">
+        <f>C2</f>
+        <v/>
+      </c>
+      <c r="E2" s="5">
+        <f>B2-D2</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2005</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <v>0.66</v>
       </c>
+      <c r="C3" s="5">
+        <f>B3-B2</f>
+        <v/>
+      </c>
+      <c r="D3" s="5">
+        <f>D2+C3</f>
+        <v/>
+      </c>
+      <c r="E3" s="5">
+        <f>B3-D3</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>2006</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>0.83</v>
       </c>
+      <c r="C4" s="5">
+        <f>B4-B3</f>
+        <v/>
+      </c>
+      <c r="D4" s="5">
+        <f>D3+C4</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
+        <f>B4-D4</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>2007</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>0.99</v>
       </c>
+      <c r="C5" s="5">
+        <f>B5-B4</f>
+        <v/>
+      </c>
+      <c r="D5" s="5">
+        <f>D4+C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="5">
+        <f>B5-D5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>2008</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>1.16</v>
       </c>
+      <c r="C6" s="5">
+        <f>B6-B5</f>
+        <v/>
+      </c>
+      <c r="D6" s="5">
+        <f>D5+C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="5">
+        <f>B6-D6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>2009</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <v>1.32</v>
       </c>
+      <c r="C7" s="5">
+        <f>B7-B6</f>
+        <v/>
+      </c>
+      <c r="D7" s="5">
+        <f>D6+C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="5">
+        <f>B7-D7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>2010</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="4" t="n">
         <v>1.49</v>
       </c>
+      <c r="C8" s="5">
+        <f>B8-B7</f>
+        <v/>
+      </c>
+      <c r="D8" s="5">
+        <f>D7+C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="5">
+        <f>B8-D8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>2011</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="4" t="n">
         <v>1.65</v>
       </c>
+      <c r="C9" s="5">
+        <f>B9-B8</f>
+        <v/>
+      </c>
+      <c r="D9" s="5">
+        <f>D8+C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="5">
+        <f>B9-D9</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>2012</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="4" t="n">
         <v>1.82</v>
       </c>
+      <c r="C10" s="5">
+        <f>B10-B9</f>
+        <v/>
+      </c>
+      <c r="D10" s="5">
+        <f>D9+C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="5">
+        <f>B10-D10</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>2013</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="4" t="n">
         <v>1.97</v>
       </c>
+      <c r="C11" s="5">
+        <f>B11-B10</f>
+        <v/>
+      </c>
+      <c r="D11" s="5">
+        <f>D10+C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>B11-D11</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>2014</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="4" t="n">
         <v>2.13</v>
       </c>
+      <c r="C12" s="5">
+        <f>B12-B11</f>
+        <v/>
+      </c>
+      <c r="D12" s="5">
+        <f>D11+C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>B12-D12</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>2015</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="4" t="n">
         <v>2.29</v>
       </c>
+      <c r="C13" s="5">
+        <f>B13-B12</f>
+        <v/>
+      </c>
+      <c r="D13" s="5">
+        <f>D12+C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>B13-D13</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>2016</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="4" t="n">
         <v>2.45</v>
       </c>
+      <c r="C14" s="5">
+        <f>B14-B13</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>D13+C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>B14-D14</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>2017</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="4" t="n">
         <v>2.6</v>
       </c>
+      <c r="C15" s="5">
+        <f>B15-B14</f>
+        <v/>
+      </c>
+      <c r="D15" s="5">
+        <f>D14+C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>B15-D15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>2018</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="4" t="n">
         <v>2.75</v>
       </c>
+      <c r="C16" s="5">
+        <f>B16-B15</f>
+        <v/>
+      </c>
+      <c r="D16" s="5">
+        <f>D15+C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>B16-D16</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>2019</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="4" t="n">
         <v>2.9</v>
       </c>
+      <c r="C17" s="5">
+        <f>B17-B16</f>
+        <v/>
+      </c>
+      <c r="D17" s="5">
+        <f>D16+C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>B17-D17</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>2020</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="4" t="n">
         <v>3.06</v>
       </c>
+      <c r="C18" s="5">
+        <f>B18-B17</f>
+        <v/>
+      </c>
+      <c r="D18" s="5">
+        <f>D17+C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="5">
+        <f>B18-D18</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="4" t="n">
         <v>3.21</v>
       </c>
+      <c r="C19" s="5">
+        <f>B19-B18</f>
+        <v/>
+      </c>
+      <c r="D19" s="5">
+        <f>D18+C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="5">
+        <f>B19-D19</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="4" t="n">
         <v>3.37</v>
       </c>
+      <c r="C20" s="5">
+        <f>B20-B19</f>
+        <v/>
+      </c>
+      <c r="D20" s="5">
+        <f>D19+C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="5">
+        <f>B20-D20</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="4" t="n">
         <v>3.54</v>
       </c>
+      <c r="C21" s="5">
+        <f>B21-B20</f>
+        <v/>
+      </c>
+      <c r="D21" s="5">
+        <f>D20+C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="5">
+        <f>B21-D21</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="4" t="n">
         <v>3.74</v>
       </c>
+      <c r="C22" s="5">
+        <f>B22-B21</f>
+        <v/>
+      </c>
+      <c r="D22" s="5">
+        <f>D21+C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="5">
+        <f>B22-D22</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>2025</v>
       </c>
-      <c r="B23" s="3" t="n">
+      <c r="B23" s="4" t="n">
         <v>3.92</v>
       </c>
+      <c r="C23" s="5">
+        <f>B23-B22</f>
+        <v/>
+      </c>
+      <c r="D23" s="5">
+        <f>D22+C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="5">
+        <f>B23-D23</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>2026</v>
       </c>
-      <c r="B24" s="3" t="n">
+      <c r="B24" s="4" t="n">
         <v>4.1</v>
       </c>
+      <c r="C24" s="5">
+        <f>B24-B23</f>
+        <v/>
+      </c>
+      <c r="D24" s="5">
+        <f>D23+C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="5">
+        <f>B24-D24</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>2027</v>
       </c>
-      <c r="B25" s="3" t="n">
+      <c r="B25" s="4" t="n">
         <v>4.27</v>
       </c>
+      <c r="C25" s="5">
+        <f>B25-B24</f>
+        <v/>
+      </c>
+      <c r="D25" s="5">
+        <f>D24+C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="5">
+        <f>B25-D25</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>2028</v>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="4" t="n">
         <v>4.46</v>
       </c>
+      <c r="C26" s="5">
+        <f>B26-B25</f>
+        <v/>
+      </c>
+      <c r="D26" s="5">
+        <f>D25+C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="5">
+        <f>B26-D26</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>2029</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="4" t="n">
         <v>4.62</v>
       </c>
+      <c r="C27" s="5">
+        <f>B27-B26</f>
+        <v/>
+      </c>
+      <c r="D27" s="5">
+        <f>D26+C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="5">
+        <f>B27-D27</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>2030</v>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="4" t="n">
         <v>4.8</v>
+      </c>
+      <c r="C28" s="5">
+        <f>B28-B27</f>
+        <v/>
+      </c>
+      <c r="D28" s="5">
+        <f>D27+C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="5">
+        <f>B28-D28</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/buckman/output/depletion/TABLE_5_La_Cienega_Springs_2025.xlsx
+++ b/buckman/output/depletion/TABLE_5_La_Cienega_Springs_2025.xlsx
@@ -901,7 +901,7 @@
         <v>2024</v>
       </c>
       <c r="B22" s="4" t="n">
-        <v>3.74</v>
+        <v>3.741411570247934</v>
       </c>
       <c r="C22" s="5">
         <f>B22-B21</f>
@@ -921,7 +921,7 @@
         <v>2025</v>
       </c>
       <c r="B23" s="4" t="n">
-        <v>3.92</v>
+        <v>3.919555041322313</v>
       </c>
       <c r="C23" s="5">
         <f>B23-B22</f>
@@ -941,7 +941,7 @@
         <v>2026</v>
       </c>
       <c r="B24" s="4" t="n">
-        <v>4.1</v>
+        <v>4.107590082644628</v>
       </c>
       <c r="C24" s="5">
         <f>B24-B23</f>
@@ -961,7 +961,7 @@
         <v>2027</v>
       </c>
       <c r="B25" s="4" t="n">
-        <v>4.27</v>
+        <v>4.286211570247934</v>
       </c>
       <c r="C25" s="5">
         <f>B25-B24</f>
@@ -981,7 +981,7 @@
         <v>2028</v>
       </c>
       <c r="B26" s="4" t="n">
-        <v>4.46</v>
+        <v>4.475813553719008</v>
       </c>
       <c r="C26" s="5">
         <f>B26-B25</f>
@@ -1001,7 +1001,7 @@
         <v>2029</v>
       </c>
       <c r="B27" s="4" t="n">
-        <v>4.62</v>
+        <v>4.642893223140495</v>
       </c>
       <c r="C27" s="5">
         <f>B27-B26</f>
@@ -1021,7 +1021,7 @@
         <v>2030</v>
       </c>
       <c r="B28" s="4" t="n">
-        <v>4.8</v>
+        <v>4.822437024793389</v>
       </c>
       <c r="C28" s="5">
         <f>B28-B27</f>
